--- a/excel-files/NAVOTAS/KAUNLARAN HIGH SCHOOL.xlsx
+++ b/excel-files/NAVOTAS/KAUNLARAN HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EA78E53-8570-D742-8C03-EF90E2BB164E}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{889AEDB1-8A0F-48E4-9A9E-9B9C7062C77D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -100,6 +100,9 @@
     <t>Music and Arts</t>
   </si>
   <si>
+    <t>CO</t>
+  </si>
+  <si>
     <t>VE</t>
   </si>
   <si>
@@ -136,183 +139,6 @@
     <t>Statistics and Probability</t>
   </si>
   <si>
-    <t>QUARTER 1</t>
-  </si>
-  <si>
-    <t>QUARTER 2</t>
-  </si>
-  <si>
-    <t>QUARTER 3</t>
-  </si>
-  <si>
-    <t>QUARTER 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity based on Target LAS - Q1 </t>
-  </si>
-  <si>
-    <t>Quantity based on Target LAS - Q3</t>
-  </si>
-  <si>
-    <t>Quantity based on Target LAS - Q2</t>
-  </si>
-  <si>
-    <t>Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) Q2</t>
-  </si>
-  <si>
-    <t>Year of Delivery-LAS Q2</t>
-  </si>
-  <si>
-    <t>Quantity based on Target LAS - Q4</t>
-  </si>
-  <si>
-    <t>Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS)- Q4</t>
-  </si>
-  <si>
-    <t>Year of Delivery - LAS - Q4</t>
-  </si>
-  <si>
-    <t>Year of Delivery-LAS - Q3</t>
-  </si>
-  <si>
-    <t>Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q3</t>
-  </si>
-  <si>
-    <t>MAPEH</t>
-  </si>
-  <si>
-    <t>Year of Delivery-LAS - Q1</t>
-  </si>
-  <si>
-    <t>Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity based on Target ADM-SLM - Q1 </t>
-  </si>
-  <si>
-    <t>Year of Delivery - ADM-SLM - Q1</t>
-  </si>
-  <si>
-    <t>SOURCE - ADM-SLM (CO,RO, SDO) - Q1</t>
-  </si>
-  <si>
-    <t>Quantity based on Target ADM-SLM - Q2</t>
-  </si>
-  <si>
-    <t>Year of Delivery - ADM-SLM Q2</t>
-  </si>
-  <si>
-    <t>Quantity based on Target ADM-SLM - Q3</t>
-  </si>
-  <si>
-    <t>Year of Delivery - ADM-SLM - Q3</t>
-  </si>
-  <si>
-    <t>Quantity based on Target ADM-SLM - Q4</t>
-  </si>
-  <si>
-    <t>SOURCE - LAS (CO,RO, SDO) - Q1</t>
-  </si>
-  <si>
-    <t>GAP - LAS - Q1</t>
-  </si>
-  <si>
-    <t>SURPLUS - LAS - Q1</t>
-  </si>
-  <si>
-    <t>SOURCE-LAS (CO,RO, SDO) Q2</t>
-  </si>
-  <si>
-    <t>GAP - LAS -Q2</t>
-  </si>
-  <si>
-    <t>SURPLUS - LAS -Q2</t>
-  </si>
-  <si>
-    <t>SOURCE-LAS (CO,RO, SDO) - Q3</t>
-  </si>
-  <si>
-    <t>GAP - LAS - Q3</t>
-  </si>
-  <si>
-    <t>SURPLUS - LAS - Q3</t>
-  </si>
-  <si>
-    <t>SOURCE - LAS (CO,RO, SDO) - Q4</t>
-  </si>
-  <si>
-    <t>GAP - LAS - Q4</t>
-  </si>
-  <si>
-    <t>SURPLUS - LAS - Q4</t>
-  </si>
-  <si>
-    <t>GAP - ADM-SLM - Q1</t>
-  </si>
-  <si>
-    <t>SURPLUS - ADM-SLM - Q1</t>
-  </si>
-  <si>
-    <t>GAP - ADM-SLM - Q2</t>
-  </si>
-  <si>
-    <t>SOURCE - ADM-SLM (CO,RO, SDO) Q2</t>
-  </si>
-  <si>
-    <t>SURPLUS - ADM-SLM -Q2</t>
-  </si>
-  <si>
-    <t>SOURCE - ADM-SLM(CO,RO, SDO) - Q3</t>
-  </si>
-  <si>
-    <t>GAP - ADM-SLM - Q3</t>
-  </si>
-  <si>
-    <t>SURPLUS - ADM-SLM - Q3</t>
-  </si>
-  <si>
-    <t>Year of Delivery - ADM-SLM- Q4</t>
-  </si>
-  <si>
-    <t>SOURCE - ADM-SLM - (CO,RO, SDO) - Q4</t>
-  </si>
-  <si>
-    <t>GAP - ADM-SLM - Q4</t>
-  </si>
-  <si>
-    <t>SURPLUS - ADM-SLM- Q4</t>
-  </si>
-  <si>
-    <t>Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM)- Q4</t>
-  </si>
-  <si>
-    <t>Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q1</t>
-  </si>
-  <si>
-    <t>Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q2</t>
-  </si>
-  <si>
-    <t>Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q3</t>
-  </si>
-  <si>
-    <t>KINDER</t>
-  </si>
-  <si>
-    <t>PE</t>
-  </si>
-  <si>
-    <t>Music</t>
-  </si>
-  <si>
-    <t>Arts</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>CO</t>
-  </si>
-  <si>
     <t>Earth &amp; Life Science</t>
   </si>
   <si>
@@ -338,12 +164,186 @@
     <t xml:space="preserve">
 Business Finance</t>
   </si>
+  <si>
+    <t>QUARTER 1</t>
+  </si>
+  <si>
+    <t>QUARTER 2</t>
+  </si>
+  <si>
+    <t>QUARTER 3</t>
+  </si>
+  <si>
+    <t>QUARTER 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity based on Target LAS - Q1 </t>
+  </si>
+  <si>
+    <t>Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q1</t>
+  </si>
+  <si>
+    <t>Year of Delivery-LAS - Q1</t>
+  </si>
+  <si>
+    <t>SOURCE - LAS (CO,RO, SDO) - Q1</t>
+  </si>
+  <si>
+    <t>GAP - LAS - Q1</t>
+  </si>
+  <si>
+    <t>SURPLUS - LAS - Q1</t>
+  </si>
+  <si>
+    <t>Quantity based on Target LAS - Q2</t>
+  </si>
+  <si>
+    <t>Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) Q2</t>
+  </si>
+  <si>
+    <t>Year of Delivery-LAS Q2</t>
+  </si>
+  <si>
+    <t>SOURCE-LAS (CO,RO, SDO) Q2</t>
+  </si>
+  <si>
+    <t>GAP - LAS -Q2</t>
+  </si>
+  <si>
+    <t>SURPLUS - LAS -Q2</t>
+  </si>
+  <si>
+    <t>Quantity based on Target LAS - Q3</t>
+  </si>
+  <si>
+    <t>Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS) - Q3</t>
+  </si>
+  <si>
+    <t>Year of Delivery-LAS - Q3</t>
+  </si>
+  <si>
+    <t>SOURCE-LAS (CO,RO, SDO) - Q3</t>
+  </si>
+  <si>
+    <t>GAP - LAS - Q3</t>
+  </si>
+  <si>
+    <t>SURPLUS - LAS - Q3</t>
+  </si>
+  <si>
+    <t>Quantity based on Target LAS - Q4</t>
+  </si>
+  <si>
+    <t>Quantity of Learning Activity Sheets Received (Quantity received x No. of LAS)- Q4</t>
+  </si>
+  <si>
+    <t>Year of Delivery - LAS - Q4</t>
+  </si>
+  <si>
+    <t>SOURCE - LAS (CO,RO, SDO) - Q4</t>
+  </si>
+  <si>
+    <t>GAP - LAS - Q4</t>
+  </si>
+  <si>
+    <t>SURPLUS - LAS - Q4</t>
+  </si>
+  <si>
+    <t>KINDER</t>
+  </si>
+  <si>
+    <t>MAPEH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity based on Target ADM-SLM - Q1 </t>
+  </si>
+  <si>
+    <t>Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q1</t>
+  </si>
+  <si>
+    <t>Year of Delivery - ADM-SLM - Q1</t>
+  </si>
+  <si>
+    <t>SOURCE - ADM-SLM (CO,RO, SDO) - Q1</t>
+  </si>
+  <si>
+    <t>GAP - ADM-SLM - Q1</t>
+  </si>
+  <si>
+    <t>SURPLUS - ADM-SLM - Q1</t>
+  </si>
+  <si>
+    <t>Quantity based on Target ADM-SLM - Q2</t>
+  </si>
+  <si>
+    <t>Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q2</t>
+  </si>
+  <si>
+    <t>Year of Delivery - ADM-SLM Q2</t>
+  </si>
+  <si>
+    <t>SOURCE - ADM-SLM (CO,RO, SDO) Q2</t>
+  </si>
+  <si>
+    <t>GAP - ADM-SLM - Q2</t>
+  </si>
+  <si>
+    <t>SURPLUS - ADM-SLM -Q2</t>
+  </si>
+  <si>
+    <t>Quantity based on Target ADM-SLM - Q3</t>
+  </si>
+  <si>
+    <t>Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM) - Q3</t>
+  </si>
+  <si>
+    <t>Year of Delivery - ADM-SLM - Q3</t>
+  </si>
+  <si>
+    <t>SOURCE - ADM-SLM(CO,RO, SDO) - Q3</t>
+  </si>
+  <si>
+    <t>GAP - ADM-SLM - Q3</t>
+  </si>
+  <si>
+    <t>SURPLUS - ADM-SLM - Q3</t>
+  </si>
+  <si>
+    <t>Quantity based on Target ADM-SLM - Q4</t>
+  </si>
+  <si>
+    <t>Quantity of ADM-SLM Received (Quantity received x No. of ADM-SLM)- Q4</t>
+  </si>
+  <si>
+    <t>Year of Delivery - ADM-SLM- Q4</t>
+  </si>
+  <si>
+    <t>SOURCE - ADM-SLM - (CO,RO, SDO) - Q4</t>
+  </si>
+  <si>
+    <t>GAP - ADM-SLM - Q4</t>
+  </si>
+  <si>
+    <t>SURPLUS - ADM-SLM- Q4</t>
+  </si>
+  <si>
+    <t>PE</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>Music</t>
+  </si>
+  <si>
+    <t>Arts</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -407,26 +407,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Bookman Old Style"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="1"/>
-      <name val="Bookman Old Style"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color theme="1"/>
-      <name val="Bookman Old Style"/>
-      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -674,7 +654,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -737,12 +717,6 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -755,10 +729,7 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -770,39 +741,22 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -811,20 +765,23 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1898,6 +1855,13 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1921,13 +1885,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -3006,6 +2963,13 @@
       </border>
     </dxf>
     <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -3042,13 +3006,6 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -3091,7 +3048,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="61" tableBorderDxfId="60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
   <autoFilter ref="A1:H145" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
@@ -3108,7 +3065,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
   <autoFilter ref="A2:AA127" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
@@ -3164,7 +3121,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
   <autoFilter ref="A2:AA140" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="26"/>
@@ -3537,17 +3494,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H106"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.22265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.84375" customWidth="1"/>
-    <col min="3" max="5" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.1015625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.06640625" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
+    <col min="3" max="5" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
     <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -3573,7 +3530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="42.75" customHeight="1">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3593,7 +3550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="29.25" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3613,7 +3570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="21" customHeight="1">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -3633,7 +3590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="25.5" customHeight="1">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -3653,7 +3610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="20.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3673,12 +3630,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="39.75" customHeight="1">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -3698,7 +3655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="29.25" customHeight="1">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -3718,7 +3675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="28.5" customHeight="1">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -3738,7 +3695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="24" customHeight="1">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -3758,7 +3715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="20.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3778,12 +3735,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="49.5" customHeight="1">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -3803,7 +3760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="29.25" customHeight="1">
       <c r="A15" s="1">
         <v>3</v>
       </c>
@@ -3823,7 +3780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="27" customHeight="1">
       <c r="A16" s="1">
         <v>3</v>
       </c>
@@ -3843,7 +3800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="23.25" customHeight="1">
       <c r="A17" s="1">
         <v>3</v>
       </c>
@@ -3863,7 +3820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="21" customHeight="1">
       <c r="A18" s="1">
         <v>3</v>
       </c>
@@ -3883,7 +3840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="20.25">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -3903,7 +3860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -3913,7 +3870,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="28.5" customHeight="1">
       <c r="A21" s="1">
         <v>4</v>
       </c>
@@ -3933,7 +3890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="24" customHeight="1">
       <c r="A22" s="1">
         <v>4</v>
       </c>
@@ -3953,7 +3910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="20.25">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -3973,7 +3930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="27" customHeight="1">
       <c r="A24" s="1">
         <v>4</v>
       </c>
@@ -3993,7 +3950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="33.75" customHeight="1">
       <c r="A25" s="1">
         <v>4</v>
       </c>
@@ -4013,7 +3970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="33.75" customHeight="1">
       <c r="A26" s="1">
         <v>4</v>
       </c>
@@ -4033,7 +3990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="33.75" customHeight="1">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -4053,7 +4010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="27.75" customHeight="1">
       <c r="A28" s="1">
         <v>4</v>
       </c>
@@ -4073,7 +4030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="27.75" customHeight="1">
       <c r="A29" s="1">
         <v>4</v>
       </c>
@@ -4093,7 +4050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" ht="27.75" customHeight="1">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
@@ -4103,7 +4060,7 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1">
       <c r="A31" s="1">
         <v>5</v>
       </c>
@@ -4123,7 +4080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="27.75" customHeight="1">
       <c r="A32" s="1">
         <v>5</v>
       </c>
@@ -4143,7 +4100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="27.75" customHeight="1">
       <c r="A33" s="1">
         <v>5</v>
       </c>
@@ -4163,7 +4120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="27.75" customHeight="1">
       <c r="A34" s="1">
         <v>5</v>
       </c>
@@ -4183,7 +4140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="39" customHeight="1">
       <c r="A35" s="1">
         <v>5</v>
       </c>
@@ -4203,7 +4160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="27.75" customHeight="1">
       <c r="A36" s="1">
         <v>5</v>
       </c>
@@ -4223,7 +4180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="27.75" customHeight="1">
       <c r="A37" s="1">
         <v>5</v>
       </c>
@@ -4243,7 +4200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="27.75" customHeight="1">
       <c r="A38" s="1">
         <v>5</v>
       </c>
@@ -4263,7 +4220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="27.75" customHeight="1">
       <c r="A39" s="1">
         <v>5</v>
       </c>
@@ -4283,7 +4240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" ht="27.75" customHeight="1">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
@@ -4293,7 +4250,7 @@
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="27.75" customHeight="1">
       <c r="A41" s="1">
         <v>6</v>
       </c>
@@ -4313,7 +4270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="27.75" customHeight="1">
       <c r="A42" s="1">
         <v>6</v>
       </c>
@@ -4333,7 +4290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="27.75" customHeight="1">
       <c r="A43" s="1">
         <v>6</v>
       </c>
@@ -4353,7 +4310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="27.75" customHeight="1">
       <c r="A44" s="1">
         <v>6</v>
       </c>
@@ -4373,7 +4330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="36.75" customHeight="1">
       <c r="A45" s="1">
         <v>6</v>
       </c>
@@ -4393,7 +4350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="27.75" customHeight="1">
       <c r="A46" s="1">
         <v>6</v>
       </c>
@@ -4413,7 +4370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="27.75" customHeight="1">
       <c r="A47" s="1">
         <v>6</v>
       </c>
@@ -4433,7 +4390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="27.75" customHeight="1">
       <c r="A48" s="1">
         <v>6</v>
       </c>
@@ -4453,7 +4410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="27.75" customHeight="1">
       <c r="A49" s="1">
         <v>6</v>
       </c>
@@ -4473,7 +4430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" ht="27.75" customHeight="1">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
@@ -4483,7 +4440,7 @@
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="27.75" customHeight="1">
       <c r="A51" s="10">
         <v>7</v>
       </c>
@@ -4500,7 +4457,7 @@
         <v>2025</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G51" s="3">
         <f t="shared" ref="G51:G59" si="10">IF((C51-D51)&lt;0,0,C51-D51)</f>
@@ -4511,7 +4468,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="27.75" customHeight="1">
       <c r="A52" s="10">
         <v>7</v>
       </c>
@@ -4531,7 +4488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="27.75" customHeight="1">
       <c r="A53" s="10">
         <v>7</v>
       </c>
@@ -4548,7 +4505,7 @@
         <v>2024</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G53" s="3">
         <f t="shared" si="10"/>
@@ -4559,12 +4516,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="27.75" customHeight="1">
       <c r="A54" s="10">
         <v>7</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C54" s="10"/>
       <c r="D54" s="10"/>
@@ -4579,7 +4536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="39" customHeight="1">
       <c r="A55" s="10">
         <v>7</v>
       </c>
@@ -4596,7 +4553,7 @@
         <v>2025</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G55" s="3">
         <f t="shared" si="10"/>
@@ -4607,7 +4564,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="27.75" customHeight="1">
       <c r="A56" s="10">
         <v>7</v>
       </c>
@@ -4624,7 +4581,7 @@
         <v>2024</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G56" s="3">
         <f t="shared" si="10"/>
@@ -4635,7 +4592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="27.75" customHeight="1">
       <c r="A57" s="10">
         <v>7</v>
       </c>
@@ -4652,7 +4609,7 @@
         <v>2025</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G57" s="3">
         <f t="shared" si="10"/>
@@ -4663,12 +4620,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="27.75" customHeight="1">
       <c r="A58" s="10">
         <v>7</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C58" s="10">
         <v>996</v>
@@ -4680,7 +4637,7 @@
         <v>2025</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G58" s="3">
         <f t="shared" si="10"/>
@@ -4691,7 +4648,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="27.75" customHeight="1">
       <c r="A59" s="10">
         <v>7</v>
       </c>
@@ -4708,7 +4665,7 @@
         <v>2025</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G59" s="3">
         <f t="shared" si="10"/>
@@ -4719,7 +4676,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" ht="27.75" customHeight="1">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8"/>
@@ -4729,7 +4686,7 @@
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="27.75" customHeight="1">
       <c r="A61" s="10">
         <v>8</v>
       </c>
@@ -4749,7 +4706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="27.75" customHeight="1">
       <c r="A62" s="10">
         <v>8</v>
       </c>
@@ -4769,7 +4726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="27.75" customHeight="1">
       <c r="A63" s="10">
         <v>8</v>
       </c>
@@ -4786,7 +4743,7 @@
         <v>2025</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G63" s="3">
         <f t="shared" si="12"/>
@@ -4797,12 +4754,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="27.75" customHeight="1">
       <c r="A64" s="10">
         <v>8</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C64" s="10">
         <v>1032</v>
@@ -4814,7 +4771,7 @@
         <v>2025</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G64" s="3">
         <f t="shared" si="12"/>
@@ -4825,12 +4782,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" ht="27.75" customHeight="1">
       <c r="A65" s="10">
         <v>8</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
@@ -4845,7 +4802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ht="27.75" customHeight="1">
       <c r="A66" s="10">
         <v>8</v>
       </c>
@@ -4865,7 +4822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="27.75" customHeight="1">
       <c r="A67" s="10">
         <v>8</v>
       </c>
@@ -4885,12 +4842,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="27.75" customHeight="1">
       <c r="A68" s="10">
         <v>8</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="10"/>
@@ -4905,7 +4862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="27.75" customHeight="1">
       <c r="A69" s="10">
         <v>8</v>
       </c>
@@ -4925,7 +4882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" ht="27.75" customHeight="1">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
@@ -4935,7 +4892,7 @@
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="27.75" customHeight="1">
       <c r="A71" s="10">
         <v>9</v>
       </c>
@@ -4955,7 +4912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="27.75" customHeight="1">
       <c r="A72" s="10">
         <v>9</v>
       </c>
@@ -4975,7 +4932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="27.75" customHeight="1">
       <c r="A73" s="10">
         <v>9</v>
       </c>
@@ -4995,12 +4952,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="27.75" customHeight="1">
       <c r="A74" s="10">
         <v>9</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="10"/>
@@ -5015,12 +4972,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="27.75" customHeight="1">
       <c r="A75" s="10">
         <v>9</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
@@ -5035,7 +4992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" ht="27.75" customHeight="1">
       <c r="A76" s="10">
         <v>9</v>
       </c>
@@ -5055,7 +5012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" ht="27.75" customHeight="1">
       <c r="A77" s="10">
         <v>9</v>
       </c>
@@ -5075,12 +5032,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" ht="27.75" customHeight="1">
       <c r="A78" s="10">
         <v>9</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="10"/>
@@ -5095,7 +5052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" ht="27.75" customHeight="1">
       <c r="A79" s="10">
         <v>9</v>
       </c>
@@ -5115,7 +5072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" ht="27.75" customHeight="1">
       <c r="A80" s="7"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -5125,7 +5082,7 @@
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="27.75" customHeight="1">
       <c r="A81" s="10">
         <v>10</v>
       </c>
@@ -5145,7 +5102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" ht="27.75" customHeight="1">
       <c r="A82" s="10">
         <v>10</v>
       </c>
@@ -5165,7 +5122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="27.75" customHeight="1">
       <c r="A83" s="10">
         <v>10</v>
       </c>
@@ -5185,12 +5142,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" ht="27.75" customHeight="1">
       <c r="A84" s="10">
         <v>10</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="10"/>
@@ -5205,12 +5162,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" ht="27.75" customHeight="1">
       <c r="A85" s="10">
         <v>10</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="10"/>
@@ -5225,7 +5182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="27.75" customHeight="1">
       <c r="A86" s="10">
         <v>10</v>
       </c>
@@ -5245,7 +5202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" ht="27.75" customHeight="1">
       <c r="A87" s="10">
         <v>10</v>
       </c>
@@ -5265,12 +5222,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" ht="27.75" customHeight="1">
       <c r="A88" s="10">
         <v>10</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="10"/>
@@ -5285,7 +5242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ht="27.75" customHeight="1">
       <c r="A89" s="10">
         <v>10</v>
       </c>
@@ -5305,7 +5262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" ht="27.75" customHeight="1">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
@@ -5315,12 +5272,12 @@
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" ht="39.75" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="1">
@@ -5330,7 +5287,7 @@
         <v>2024</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G91" s="3">
         <f t="shared" ref="G91:G98" si="18">IF((C91-D91)&lt;0,0,C91-D91)</f>
@@ -5341,12 +5298,12 @@
         <v>622</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" ht="27.75" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
@@ -5361,12 +5318,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" ht="27.75" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1">
@@ -5376,7 +5333,7 @@
         <v>2024</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G93" s="3">
         <f t="shared" si="18"/>
@@ -5387,12 +5344,12 @@
         <v>534</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" ht="27.75" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1">
@@ -5402,7 +5359,7 @@
         <v>2025</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G94" s="3">
         <f t="shared" si="18"/>
@@ -5413,12 +5370,12 @@
         <v>622</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" ht="40.5" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1">
@@ -5428,7 +5385,7 @@
         <v>2025</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G95" s="3">
         <f t="shared" si="18"/>
@@ -5439,12 +5396,12 @@
         <v>622</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" ht="38.25" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="1">
@@ -5454,7 +5411,7 @@
         <v>2025</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G96" s="3">
         <f t="shared" si="18"/>
@@ -5465,12 +5422,12 @@
         <v>622</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" ht="27.75" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="1">
@@ -5480,7 +5437,7 @@
         <v>2025</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G97" s="3">
         <f t="shared" si="18"/>
@@ -5491,12 +5448,12 @@
         <v>622</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" ht="47.25" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1">
@@ -5506,7 +5463,7 @@
         <v>2025</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G98" s="3">
         <f t="shared" si="18"/>
@@ -5517,12 +5474,12 @@
         <v>622</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" ht="20.25">
       <c r="A99" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="C99" s="1"/>
       <c r="D99" s="1">
@@ -5532,7 +5489,7 @@
         <v>2024</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G99" s="3">
         <f>IF((C99-D99)&lt;0,0,C99-D99)</f>
@@ -5543,12 +5500,12 @@
         <v>616</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="68.25" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" ht="68.25">
       <c r="A100" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="C100" s="1"/>
       <c r="D100" s="1">
@@ -5558,7 +5515,7 @@
         <v>2025</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G100" s="3">
         <f>IF((C100-D100)&lt;0,0,C100-D100)</f>
@@ -5569,12 +5526,12 @@
         <v>622</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" ht="20.25">
       <c r="A101" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="C101" s="1"/>
       <c r="D101" s="1">
@@ -5584,7 +5541,7 @@
         <v>2024</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G101" s="3">
         <f>IF((C101-D101)&lt;0,0,C101-D101)</f>
@@ -5595,12 +5552,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" ht="34.5">
       <c r="A102" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>94</v>
+        <v>36</v>
       </c>
       <c r="C102" s="1"/>
       <c r="D102" s="1">
@@ -5610,7 +5567,7 @@
         <v>2024</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G102" s="3">
         <f>IF((C102-D102)&lt;0,0,C102-D102)</f>
@@ -5621,12 +5578,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="68.25" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" ht="68.25">
       <c r="A103" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="1">
@@ -5636,7 +5593,7 @@
         <v>2024</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G103" s="3">
         <f>IF((C103-D103)&lt;0,0,C103-D103)</f>
@@ -5647,12 +5604,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="51.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" ht="51.75">
       <c r="A104" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="1">
@@ -5662,7 +5619,7 @@
         <v>2024</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G104" s="3">
         <f>IF((C104-D104)&lt;0,0,C104-D104)</f>
@@ -5673,12 +5630,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="85.5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" ht="85.5">
       <c r="A105" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="1">
@@ -5688,7 +5645,7 @@
         <v>2024</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G105" s="3">
         <f>IF((C105-D105)&lt;0,0,C105-D105)</f>
@@ -5699,12 +5656,12 @@
         <v>205</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="51.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" ht="51.75">
       <c r="A106" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="1">
@@ -5714,7 +5671,7 @@
         <v>2024</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G106" s="3">
         <f>IF((C106-D106)&lt;0,0,C106-D106)</f>
@@ -5732,8 +5689,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E91:E106 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E51:E59" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E106 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F91:F106 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F51:F59" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5748,70 +5705,70 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AA127"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.4140625" customWidth="1"/>
-    <col min="2" max="2" width="27.84375" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
-    <col min="4" max="4" width="26.23046875" customWidth="1"/>
-    <col min="5" max="5" width="23.13671875" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5625" customWidth="1"/>
-    <col min="8" max="9" width="20.84765625" customWidth="1"/>
-    <col min="10" max="10" width="13.71875" customWidth="1"/>
-    <col min="11" max="11" width="35.6484375" customWidth="1"/>
-    <col min="12" max="12" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="31.609375" customWidth="1"/>
-    <col min="14" max="15" width="20.84765625" customWidth="1"/>
-    <col min="16" max="16" width="21.65625" customWidth="1"/>
-    <col min="17" max="17" width="33.359375" customWidth="1"/>
-    <col min="18" max="18" width="25.828125" customWidth="1"/>
-    <col min="19" max="19" width="32.95703125" customWidth="1"/>
-    <col min="20" max="21" width="20.84765625" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" customWidth="1"/>
+    <col min="5" max="5" width="23.140625" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" customWidth="1"/>
+    <col min="8" max="9" width="20.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="35.7109375" customWidth="1"/>
+    <col min="12" max="12" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.5703125" customWidth="1"/>
+    <col min="14" max="15" width="20.85546875" customWidth="1"/>
+    <col min="16" max="16" width="21.7109375" customWidth="1"/>
+    <col min="17" max="17" width="33.42578125" customWidth="1"/>
+    <col min="18" max="18" width="25.85546875" customWidth="1"/>
+    <col min="19" max="19" width="33" customWidth="1"/>
+    <col min="20" max="21" width="20.85546875" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25.01953125" customWidth="1"/>
-    <col min="24" max="24" width="15.33203125" customWidth="1"/>
-    <col min="25" max="25" width="20.84765625" customWidth="1"/>
-    <col min="26" max="26" width="14.796875" customWidth="1"/>
-    <col min="27" max="27" width="15.19921875" customWidth="1"/>
+    <col min="23" max="23" width="25" customWidth="1"/>
+    <col min="24" max="24" width="15.28515625" customWidth="1"/>
+    <col min="25" max="25" width="20.85546875" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="31" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="53" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="54" t="s">
-        <v>35</v>
-      </c>
-      <c r="W1" s="54"/>
-      <c r="X1" s="54"/>
-      <c r="Y1" s="54"/>
-      <c r="Z1" s="54"/>
-      <c r="AA1" s="54"/>
-    </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+      <c r="D1" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="42"/>
+      <c r="V1" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="W1" s="43"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="43"/>
+      <c r="AA1" s="43"/>
+    </row>
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -5822,106 +5779,106 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F2" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="G2" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="K2" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="M2" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="N2" s="44" t="s">
+        <v>55</v>
+      </c>
+      <c r="O2" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="P2" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="Q2" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="26" t="s">
+      <c r="R2" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="J2" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="K2" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="L2" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="M2" s="24" t="s">
+      <c r="S2" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="N2" s="24" t="s">
+      <c r="T2" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="O2" s="22" t="s">
+      <c r="U2" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="P2" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q2" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="R2" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="S2" s="25" t="s">
+      <c r="V2" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="T2" s="25" t="s">
+      <c r="W2" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="U2" s="26" t="s">
+      <c r="X2" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="V2" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="W2" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="X2" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y2" s="30" t="s">
+      <c r="Y2" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="Z2" s="30" t="s">
+      <c r="Z2" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="AA2" s="28" t="s">
+      <c r="AA2" s="26" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="40">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="40"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="41">
+    <row r="3" spans="1:27" ht="30.6" customHeight="1">
+      <c r="A3" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="34"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34">
         <f>IF((D3-E3)&lt;0,0,(D3-E3))</f>
         <v>0</v>
       </c>
-      <c r="I3" s="41">
+      <c r="I3" s="34">
         <f>IF((E3-D3)&lt;0,0,(E3-D3))</f>
         <v>0</v>
       </c>
-      <c r="J3" s="40">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="40"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="40"/>
+      <c r="J3" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="34"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="34"/>
       <c r="N3" s="5">
         <f t="shared" ref="N3" si="0">IF((J3-K3)&lt;0,0,(J3-K3))</f>
         <v>0</v>
@@ -5934,34 +5891,34 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="38"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40">
+      <c r="Q3" s="34"/>
+      <c r="R3" s="32"/>
+      <c r="S3" s="34"/>
+      <c r="T3" s="34">
         <f>IF((P3-Q3)&lt;0,0,(P3-Q3))</f>
         <v>0</v>
       </c>
-      <c r="U3" s="40">
+      <c r="U3" s="34">
         <f>IF((Q3-P3)&lt;0,0,(Q3-P3))</f>
         <v>0</v>
       </c>
-      <c r="V3" s="40">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="W3" s="40"/>
-      <c r="X3" s="38"/>
-      <c r="Y3" s="40"/>
-      <c r="Z3" s="40">
+      <c r="V3" s="34">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="W3" s="34"/>
+      <c r="X3" s="32"/>
+      <c r="Y3" s="34"/>
+      <c r="Z3" s="34">
         <f>IF((V3-W3)&lt;0,0,(V3-W3))</f>
         <v>0</v>
       </c>
-      <c r="AA3" s="40">
+      <c r="AA3" s="34">
         <f>IF((W3-V3)&lt;0,0,(W3-V3))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
@@ -5973,7 +5930,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="34.5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -6042,7 +5999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="20.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -6111,7 +6068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="20.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -6180,7 +6137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="20.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -6249,7 +6206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="20.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -6318,26 +6275,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A10" s="35">
+    <row r="10" spans="1:27" ht="20.25">
+      <c r="A10" s="1">
         <v>1</v>
       </c>
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="37">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="35"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="1"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="37">
+      <c r="H10" s="5">
         <f>IF((D10-E10)&lt;0,0,(D10-E10))</f>
         <v>0</v>
       </c>
-      <c r="I10" s="37">
+      <c r="I10" s="5">
         <f>IF((E10-D10)&lt;0,0,(E10-D10))</f>
         <v>0</v>
       </c>
@@ -6345,8 +6302,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K10" s="37"/>
-      <c r="L10" s="35"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="1"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5">
         <f t="shared" si="10"/>
@@ -6360,8 +6317,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="35"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="1"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
         <f t="shared" si="12"/>
@@ -6375,8 +6332,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W10" s="37"/>
-      <c r="X10" s="35"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="1"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5">
         <f t="shared" si="14"/>
@@ -6387,26 +6344,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="35">
+    <row r="11" spans="1:27" ht="20.25">
+      <c r="A11" s="1">
         <v>1</v>
       </c>
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="37">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="37"/>
-      <c r="F11" s="35"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="1"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="37">
+      <c r="H11" s="5">
         <f>IF((D11-E11)&lt;0,0,(D11-E11))</f>
         <v>0</v>
       </c>
-      <c r="I11" s="37">
+      <c r="I11" s="5">
         <f>IF((E11-D11)&lt;0,0,(E11-D11))</f>
         <v>0</v>
       </c>
@@ -6414,8 +6371,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K11" s="37"/>
-      <c r="L11" s="35"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="1"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5">
         <f t="shared" si="10"/>
@@ -6429,8 +6386,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="37"/>
-      <c r="R11" s="35"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="1"/>
       <c r="S11" s="5"/>
       <c r="T11" s="5">
         <f t="shared" si="12"/>
@@ -6444,8 +6401,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W11" s="37"/>
-      <c r="X11" s="35"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="1"/>
       <c r="Y11" s="5"/>
       <c r="Z11" s="5">
         <f t="shared" si="14"/>
@@ -6456,26 +6413,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A12" s="35">
+    <row r="12" spans="1:27" ht="20.25">
+      <c r="A12" s="1">
         <v>1</v>
       </c>
-      <c r="B12" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="35"/>
-      <c r="D12" s="37">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="37"/>
-      <c r="F12" s="35"/>
+      <c r="B12" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="1"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="37">
+      <c r="H12" s="5">
         <f>IF((D12-E12)&lt;0,0,(D12-E12))</f>
         <v>0</v>
       </c>
-      <c r="I12" s="37">
+      <c r="I12" s="5">
         <f>IF((E12-D12)&lt;0,0,(E12-D12))</f>
         <v>0</v>
       </c>
@@ -6483,8 +6440,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K12" s="37"/>
-      <c r="L12" s="35"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="1"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5">
         <f t="shared" si="10"/>
@@ -6498,8 +6455,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="35"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="1"/>
       <c r="S12" s="5"/>
       <c r="T12" s="5">
         <f t="shared" si="12"/>
@@ -6513,8 +6470,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W12" s="37"/>
-      <c r="X12" s="35"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="1"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5">
         <f t="shared" si="14"/>
@@ -6525,7 +6482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6538,7 +6495,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="34.5">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6607,7 +6564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="20.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6676,7 +6633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="20.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6745,7 +6702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="20.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6814,7 +6771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="20.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6883,26 +6840,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A19" s="35">
+    <row r="19" spans="1:27" ht="20.25">
+      <c r="A19" s="1">
         <v>2</v>
       </c>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="37">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="37"/>
-      <c r="F19" s="35"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="1"/>
       <c r="G19" s="5"/>
-      <c r="H19" s="37">
+      <c r="H19" s="5">
         <f>IF((D19-E19)&lt;0,0,(D19-E19))</f>
         <v>0</v>
       </c>
-      <c r="I19" s="37">
+      <c r="I19" s="5">
         <f>IF((E19-D19)&lt;0,0,(E19-D19))</f>
         <v>0</v>
       </c>
@@ -6910,8 +6867,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K19" s="37"/>
-      <c r="L19" s="35"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="1"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5">
         <f t="shared" si="10"/>
@@ -6925,8 +6882,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="37"/>
-      <c r="R19" s="35"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="1"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
         <f t="shared" si="12"/>
@@ -6940,8 +6897,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W19" s="37"/>
-      <c r="X19" s="35"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="1"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="5">
         <f t="shared" si="14"/>
@@ -6952,26 +6909,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A20" s="35">
+    <row r="20" spans="1:27" ht="20.25">
+      <c r="A20" s="1">
         <v>2</v>
       </c>
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="37">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="37"/>
-      <c r="F20" s="35"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="1"/>
       <c r="G20" s="5"/>
-      <c r="H20" s="37">
+      <c r="H20" s="5">
         <f>IF((D20-E20)&lt;0,0,(D20-E20))</f>
         <v>0</v>
       </c>
-      <c r="I20" s="37">
+      <c r="I20" s="5">
         <f>IF((E20-D20)&lt;0,0,(E20-D20))</f>
         <v>0</v>
       </c>
@@ -6979,8 +6936,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K20" s="37"/>
-      <c r="L20" s="35"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="1"/>
       <c r="M20" s="5"/>
       <c r="N20" s="5">
         <f t="shared" si="10"/>
@@ -6994,8 +6951,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q20" s="37"/>
-      <c r="R20" s="35"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="1"/>
       <c r="S20" s="5"/>
       <c r="T20" s="5">
         <f t="shared" si="12"/>
@@ -7009,8 +6966,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W20" s="37"/>
-      <c r="X20" s="35"/>
+      <c r="W20" s="5"/>
+      <c r="X20" s="1"/>
       <c r="Y20" s="5"/>
       <c r="Z20" s="5">
         <f t="shared" si="14"/>
@@ -7021,26 +6978,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A21" s="35">
+    <row r="21" spans="1:27" ht="20.25">
+      <c r="A21" s="1">
         <v>2</v>
       </c>
-      <c r="B21" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="35"/>
-      <c r="D21" s="37">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="37"/>
-      <c r="F21" s="35"/>
+      <c r="B21" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="1"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="37">
+      <c r="H21" s="5">
         <f>IF((D21-E21)&lt;0,0,(D21-E21))</f>
         <v>0</v>
       </c>
-      <c r="I21" s="37">
+      <c r="I21" s="5">
         <f>IF((E21-D21)&lt;0,0,(E21-D21))</f>
         <v>0</v>
       </c>
@@ -7048,8 +7005,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K21" s="37"/>
-      <c r="L21" s="35"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="1"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5">
         <f t="shared" si="10"/>
@@ -7063,8 +7020,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q21" s="37"/>
-      <c r="R21" s="35"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="1"/>
       <c r="S21" s="5"/>
       <c r="T21" s="5">
         <f t="shared" si="12"/>
@@ -7078,8 +7035,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W21" s="37"/>
-      <c r="X21" s="35"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="1"/>
       <c r="Y21" s="5"/>
       <c r="Z21" s="5">
         <f t="shared" si="14"/>
@@ -7090,7 +7047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -7104,7 +7061,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="34.5">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -7173,7 +7130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="20.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -7242,7 +7199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="20.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -7311,7 +7268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="20.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7380,7 +7337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="20.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7449,7 +7406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="20.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7518,26 +7475,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A29" s="35">
+    <row r="29" spans="1:27" ht="20.25">
+      <c r="A29" s="1">
         <v>3</v>
       </c>
-      <c r="B29" s="36" t="s">
+      <c r="B29" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="35"/>
-      <c r="D29" s="37">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="37"/>
-      <c r="F29" s="35"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="5"/>
+      <c r="F29" s="1"/>
       <c r="G29" s="5"/>
-      <c r="H29" s="37">
+      <c r="H29" s="5">
         <f>IF((D29-E29)&lt;0,0,(D29-E29))</f>
         <v>0</v>
       </c>
-      <c r="I29" s="37">
+      <c r="I29" s="5">
         <f>IF((E29-D29)&lt;0,0,(E29-D29))</f>
         <v>0</v>
       </c>
@@ -7545,8 +7502,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K29" s="37"/>
-      <c r="L29" s="35"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="1"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5">
         <f t="shared" si="10"/>
@@ -7560,8 +7517,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q29" s="37"/>
-      <c r="R29" s="35"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="1"/>
       <c r="S29" s="5"/>
       <c r="T29" s="5">
         <f t="shared" si="12"/>
@@ -7575,8 +7532,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W29" s="37"/>
-      <c r="X29" s="35"/>
+      <c r="W29" s="5"/>
+      <c r="X29" s="1"/>
       <c r="Y29" s="5"/>
       <c r="Z29" s="5">
         <f t="shared" si="14"/>
@@ -7587,26 +7544,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A30" s="35">
+    <row r="30" spans="1:27" ht="20.25">
+      <c r="A30" s="1">
         <v>3</v>
       </c>
-      <c r="B30" s="36" t="s">
+      <c r="B30" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="35"/>
-      <c r="D30" s="37">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="37"/>
-      <c r="F30" s="35"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="5"/>
+      <c r="F30" s="1"/>
       <c r="G30" s="5"/>
-      <c r="H30" s="37">
+      <c r="H30" s="5">
         <f>IF((D30-E30)&lt;0,0,(D30-E30))</f>
         <v>0</v>
       </c>
-      <c r="I30" s="37">
+      <c r="I30" s="5">
         <f>IF((E30-D30)&lt;0,0,(E30-D30))</f>
         <v>0</v>
       </c>
@@ -7614,8 +7571,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K30" s="37"/>
-      <c r="L30" s="35"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="1"/>
       <c r="M30" s="5"/>
       <c r="N30" s="5">
         <f t="shared" si="10"/>
@@ -7629,8 +7586,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q30" s="37"/>
-      <c r="R30" s="35"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="1"/>
       <c r="S30" s="5"/>
       <c r="T30" s="5">
         <f t="shared" si="12"/>
@@ -7644,8 +7601,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W30" s="37"/>
-      <c r="X30" s="35"/>
+      <c r="W30" s="5"/>
+      <c r="X30" s="1"/>
       <c r="Y30" s="5"/>
       <c r="Z30" s="5">
         <f t="shared" si="14"/>
@@ -7656,26 +7613,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A31" s="35">
+    <row r="31" spans="1:27" ht="20.25">
+      <c r="A31" s="1">
         <v>3</v>
       </c>
-      <c r="B31" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" s="35"/>
-      <c r="D31" s="37">
-        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E31" s="37"/>
-      <c r="F31" s="35"/>
+      <c r="B31" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="5">
+        <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="5"/>
+      <c r="F31" s="1"/>
       <c r="G31" s="5"/>
-      <c r="H31" s="37">
+      <c r="H31" s="5">
         <f>IF((D31-E31)&lt;0,0,(D31-E31))</f>
         <v>0</v>
       </c>
-      <c r="I31" s="37">
+      <c r="I31" s="5">
         <f>IF((E31-D31)&lt;0,0,(E31-D31))</f>
         <v>0</v>
       </c>
@@ -7683,8 +7640,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K31" s="37"/>
-      <c r="L31" s="35"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="1"/>
       <c r="M31" s="5"/>
       <c r="N31" s="5">
         <f t="shared" si="10"/>
@@ -7698,8 +7655,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q31" s="37"/>
-      <c r="R31" s="35"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="1"/>
       <c r="S31" s="5"/>
       <c r="T31" s="5">
         <f t="shared" si="12"/>
@@ -7713,8 +7670,8 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W31" s="37"/>
-      <c r="X31" s="35"/>
+      <c r="W31" s="5"/>
+      <c r="X31" s="1"/>
       <c r="Y31" s="5"/>
       <c r="Z31" s="5">
         <f t="shared" si="14"/>
@@ -7725,7 +7682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7739,7 +7696,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="20.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7808,7 +7765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="20.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7877,7 +7834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="20.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7946,7 +7903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="20.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -8015,7 +7972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="20.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -8084,7 +8041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="20.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -8153,7 +8110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="20.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -8222,7 +8179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="20.25">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -8291,7 +8248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="20.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8360,7 +8317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -8374,7 +8331,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" ht="20.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8443,7 +8400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="20.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8512,7 +8469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" ht="20.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8581,7 +8538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" ht="20.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8650,7 +8607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" ht="20.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8719,7 +8676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" ht="20.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8788,7 +8745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" ht="20.25">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8857,7 +8814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" ht="20.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8926,7 +8883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" ht="20.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8995,7 +8952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -9009,7 +8966,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" ht="20.25">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -9078,7 +9035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" ht="20.25">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -9147,7 +9104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" ht="20.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -9216,7 +9173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" ht="20.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -9285,7 +9242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" ht="20.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9354,7 +9311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" ht="20.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9423,7 +9380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" ht="20.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9492,7 +9449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" ht="20.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9561,7 +9518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" ht="20.25">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9630,7 +9587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -9644,7 +9601,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" ht="20.25">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9713,7 +9670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" ht="20.25">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9782,7 +9739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" ht="20.25">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9851,12 +9808,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" ht="20.25">
       <c r="A66" s="10">
         <v>7</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="12">
@@ -9920,7 +9877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" ht="20.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9989,7 +9946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" ht="20.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -10058,7 +10015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" ht="20.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -10127,12 +10084,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" ht="20.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="12">
@@ -10196,7 +10153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" ht="20.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -10265,7 +10222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -10279,7 +10236,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" ht="20.25">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -10348,7 +10305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" ht="20.25">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10417,7 +10374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" ht="20.25">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10486,12 +10443,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" ht="20.25">
       <c r="A76" s="10">
         <v>8</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="12">
@@ -10555,12 +10512,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" ht="20.25">
       <c r="A77" s="10">
         <v>8</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="12">
@@ -10624,7 +10581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" ht="20.25">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10693,7 +10650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" ht="20.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10762,12 +10719,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" ht="20.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -10831,7 +10788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" ht="20.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10900,7 +10857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10914,7 +10871,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" ht="20.25">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -10983,7 +10940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" ht="20.25">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -11052,7 +11009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" ht="20.25">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -11121,12 +11078,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" ht="20.25">
       <c r="A86" s="10">
         <v>9</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="12">
@@ -11190,12 +11147,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" ht="20.25">
       <c r="A87" s="10">
         <v>9</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="12">
@@ -11259,7 +11216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" ht="20.25">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -11328,7 +11285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" ht="20.25">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11397,12 +11354,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" ht="20.25">
       <c r="A90" s="10">
         <v>9</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C90" s="10"/>
       <c r="D90" s="12">
@@ -11466,7 +11423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:27" ht="20.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11535,7 +11492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11549,7 +11506,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" ht="20.25">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11618,7 +11575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" ht="20.25">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11687,7 +11644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" ht="20.25">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11756,12 +11713,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" ht="20.25">
       <c r="A96" s="10">
         <v>10</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="12">
@@ -11825,12 +11782,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" ht="20.25">
       <c r="A97" s="10">
         <v>10</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="12">
@@ -11894,7 +11851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" ht="20.25">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -11963,7 +11920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" ht="20.25">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -12032,12 +11989,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" ht="20.25">
       <c r="A100" s="10">
         <v>10</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -12101,7 +12058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" ht="20.25">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -12170,7 +12127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -12184,12 +12141,12 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:27" ht="34.5">
       <c r="A103" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="5">
@@ -12253,12 +12210,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" ht="20.25">
       <c r="A104" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="5">
@@ -12322,12 +12279,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" ht="20.25">
       <c r="A105" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="5">
@@ -12391,12 +12348,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" ht="20.25">
       <c r="A106" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="5">
@@ -12460,12 +12417,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" ht="34.5">
       <c r="A107" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="5">
@@ -12529,12 +12486,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" ht="34.5">
       <c r="A108" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="5">
@@ -12598,12 +12555,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" ht="34.5">
       <c r="A109" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="5">
@@ -12667,12 +12624,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" ht="34.5">
       <c r="A110" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="5">
@@ -12736,7 +12693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="20.25">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12747,7 +12704,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:27" ht="20.25">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -12809,7 +12766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:27" ht="20.25">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12871,7 +12828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:27" ht="20.25">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -12933,7 +12890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:27" ht="20.25">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -12995,7 +12952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:27" ht="20.25">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -13057,7 +13014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:27" ht="20.25">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -13119,7 +13076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:27" ht="20.25">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -13181,7 +13138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:27" ht="20.25">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -13243,7 +13200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:27" ht="20.25">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -13305,7 +13262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:27" ht="20.25">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13367,7 +13324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:27" ht="20.25">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13429,7 +13386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:27" ht="20.25">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13491,7 +13448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:27" ht="20.25">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13553,7 +13510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:27" ht="20.25">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13615,7 +13572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:27" ht="20.25">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13677,14 +13634,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A127" s="32"/>
-      <c r="B127" s="33"/>
-      <c r="C127" s="32"/>
+    <row r="127" spans="1:27" ht="20.25">
+      <c r="A127" s="29"/>
+      <c r="B127" s="30"/>
+      <c r="C127" s="29"/>
       <c r="D127" s="5"/>
-      <c r="E127" s="34"/>
-      <c r="F127" s="32"/>
-      <c r="G127" s="34"/>
+      <c r="E127" s="31"/>
+      <c r="F127" s="29"/>
+      <c r="G127" s="31"/>
       <c r="H127" s="5">
         <f t="shared" si="22"/>
         <v>0</v>
@@ -13697,9 +13654,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K127" s="34"/>
-      <c r="L127" s="32"/>
-      <c r="M127" s="34"/>
+      <c r="K127" s="31"/>
+      <c r="L127" s="29"/>
+      <c r="M127" s="31"/>
       <c r="N127" s="5">
         <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
         <v>0</v>
@@ -13709,9 +13666,9 @@
         <v>0</v>
       </c>
       <c r="P127" s="5"/>
-      <c r="Q127" s="34"/>
-      <c r="R127" s="32"/>
-      <c r="S127" s="34"/>
+      <c r="Q127" s="31"/>
+      <c r="R127" s="29"/>
+      <c r="S127" s="31"/>
       <c r="T127" s="5">
         <f t="shared" si="18"/>
         <v>0</v>
@@ -13724,9 +13681,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W127" s="34"/>
-      <c r="X127" s="32"/>
-      <c r="Y127" s="34"/>
+      <c r="W127" s="31"/>
+      <c r="X127" s="29"/>
+      <c r="Y127" s="31"/>
       <c r="Z127" s="5">
         <f t="shared" si="20"/>
         <v>0</v>
@@ -13734,186 +13691,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -13933,8 +13710,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -13952,153 +13729,153 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AB140"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.4140625" customWidth="1"/>
-    <col min="2" max="2" width="27.84375" style="45" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
-    <col min="4" max="4" width="16.41015625" customWidth="1"/>
-    <col min="5" max="5" width="23.13671875" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5625" customWidth="1"/>
-    <col min="8" max="9" width="20.84765625" customWidth="1"/>
-    <col min="10" max="10" width="13.71875" customWidth="1"/>
-    <col min="11" max="11" width="24.34765625" customWidth="1"/>
-    <col min="12" max="12" width="18.16015625" customWidth="1"/>
-    <col min="13" max="15" width="20.84765625" customWidth="1"/>
-    <col min="16" max="16" width="21.65625" customWidth="1"/>
-    <col min="17" max="17" width="29.19140625" customWidth="1"/>
-    <col min="18" max="18" width="25.828125" customWidth="1"/>
-    <col min="19" max="19" width="32.95703125" customWidth="1"/>
-    <col min="20" max="21" width="20.84765625" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1"/>
+    <col min="5" max="5" width="23.140625" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" customWidth="1"/>
+    <col min="8" max="9" width="20.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="24.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" customWidth="1"/>
+    <col min="13" max="15" width="20.85546875" customWidth="1"/>
+    <col min="16" max="16" width="21.7109375" customWidth="1"/>
+    <col min="17" max="17" width="29.140625" customWidth="1"/>
+    <col min="18" max="18" width="25.85546875" customWidth="1"/>
+    <col min="19" max="19" width="33" customWidth="1"/>
+    <col min="20" max="21" width="20.85546875" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25.01953125" customWidth="1"/>
-    <col min="24" max="24" width="15.33203125" customWidth="1"/>
-    <col min="25" max="25" width="20.84765625" customWidth="1"/>
-    <col min="26" max="26" width="14.796875" customWidth="1"/>
-    <col min="27" max="27" width="15.19921875" customWidth="1"/>
+    <col min="23" max="23" width="25" customWidth="1"/>
+    <col min="24" max="24" width="15.28515625" customWidth="1"/>
+    <col min="25" max="25" width="20.85546875" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="31" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="42"/>
-      <c r="D1" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="53" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="54" t="s">
-        <v>35</v>
-      </c>
-      <c r="W1" s="54"/>
-      <c r="X1" s="54"/>
-      <c r="Y1" s="54"/>
-      <c r="Z1" s="54"/>
-      <c r="AA1" s="54"/>
-    </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+      <c r="B1" s="35"/>
+      <c r="D1" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q1" s="42"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="42"/>
+      <c r="U1" s="42"/>
+      <c r="V1" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="W1" s="43"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="43"/>
+      <c r="AA1" s="43"/>
+    </row>
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="36" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="16" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="E2" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="K2" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="M2" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="N2" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="O2" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="J2" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="K2" s="22" t="s">
+      <c r="P2" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="L2" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="M2" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="N2" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="O2" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="P2" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q2" s="26" t="s">
+      <c r="Q2" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="R2" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="S2" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="T2" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="U2" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="V2" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="W2" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="X2" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y2" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z2" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA2" s="28" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+      <c r="R2" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="S2" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="T2" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="U2" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="V2" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="W2" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="X2" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y2" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z2" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA2" s="26" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="34.5">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -14129,11 +13906,11 @@
       <c r="L3" s="1"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5">
-        <f t="shared" ref="N3:N72" si="2">IF((J3-K3)&lt;0,0,(J3-K3))</f>
+        <f t="shared" ref="N3:N70" si="2">IF((J3-K3)&lt;0,0,(J3-K3))</f>
         <v>0</v>
       </c>
       <c r="O3" s="5">
-        <f t="shared" ref="O3:O72" si="3">IF((K3-J3)&lt;0,0,(K3-J3))</f>
+        <f t="shared" ref="O3:O70" si="3">IF((K3-J3)&lt;0,0,(K3-J3))</f>
         <v>0</v>
       </c>
       <c r="P3" s="5">
@@ -14167,7 +13944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="20.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -14236,7 +14013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="20.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -14305,7 +14082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="20.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14374,7 +14151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="20.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14443,26 +14220,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="35">
+    <row r="8" spans="1:27" ht="20.25">
+      <c r="A8" s="1">
         <v>1</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="37">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="37"/>
-      <c r="F8" s="35"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="1"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="37">
+      <c r="H8" s="5">
         <f>IF((D8-E8)&lt;0,0,(D8-E8))</f>
         <v>0</v>
       </c>
-      <c r="I8" s="37">
+      <c r="I8" s="5">
         <f>IF((E8-D8)&lt;0,0,(E8-D8))</f>
         <v>0</v>
       </c>
@@ -14470,8 +14247,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K8" s="37"/>
-      <c r="L8" s="35"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="1"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5">
         <f t="shared" si="2"/>
@@ -14485,8 +14262,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="35"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="1"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5">
         <f t="shared" si="4"/>
@@ -14500,8 +14277,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W8" s="37"/>
-      <c r="X8" s="35"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="1"/>
       <c r="Y8" s="5"/>
       <c r="Z8" s="5">
         <f t="shared" si="6"/>
@@ -14512,26 +14289,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="35">
+    <row r="9" spans="1:27" ht="20.25">
+      <c r="A9" s="1">
         <v>1</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="37">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="37"/>
-      <c r="F9" s="35"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="1"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="37">
+      <c r="H9" s="5">
         <f>IF((D9-E9)&lt;0,0,(D9-E9))</f>
         <v>0</v>
       </c>
-      <c r="I9" s="37">
+      <c r="I9" s="5">
         <f>IF((E9-D9)&lt;0,0,(E9-D9))</f>
         <v>0</v>
       </c>
@@ -14539,8 +14316,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K9" s="37"/>
-      <c r="L9" s="35"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="1"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5">
         <f t="shared" si="2"/>
@@ -14554,8 +14331,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="37"/>
-      <c r="R9" s="35"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="1"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5">
         <f t="shared" si="4"/>
@@ -14569,8 +14346,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W9" s="37"/>
-      <c r="X9" s="35"/>
+      <c r="W9" s="5"/>
+      <c r="X9" s="1"/>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5">
         <f t="shared" si="6"/>
@@ -14581,26 +14358,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A10" s="35">
+    <row r="10" spans="1:27" ht="20.25">
+      <c r="A10" s="1">
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="37">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="35"/>
+        <v>70</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="1"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="37">
+      <c r="H10" s="5">
         <f>IF((D10-E10)&lt;0,0,(D10-E10))</f>
         <v>0</v>
       </c>
-      <c r="I10" s="37">
+      <c r="I10" s="5">
         <f>IF((E10-D10)&lt;0,0,(E10-D10))</f>
         <v>0</v>
       </c>
@@ -14608,8 +14385,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K10" s="37"/>
-      <c r="L10" s="35"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="1"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5">
         <f t="shared" si="2"/>
@@ -14623,8 +14400,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="35"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="1"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
         <f t="shared" si="4"/>
@@ -14638,8 +14415,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W10" s="37"/>
-      <c r="X10" s="35"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="1"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5">
         <f t="shared" si="6"/>
@@ -14650,10 +14427,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="44"/>
-    </row>
-    <row r="12" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" s="7" customFormat="1"/>
+    <row r="12" spans="1:27" ht="34.5">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14722,7 +14497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="20.25">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14791,7 +14566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="20.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14860,7 +14635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="20.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14929,7 +14704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="20.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14998,26 +14773,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A17" s="35">
+    <row r="17" spans="1:27" ht="20.25">
+      <c r="A17" s="1">
         <v>2</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="35"/>
-      <c r="D17" s="37">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="37"/>
-      <c r="F17" s="35"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="1"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="37">
+      <c r="H17" s="5">
         <f>IF((D17-E17)&lt;0,0,(D17-E17))</f>
         <v>0</v>
       </c>
-      <c r="I17" s="37">
+      <c r="I17" s="5">
         <f>IF((E17-D17)&lt;0,0,(E17-D17))</f>
         <v>0</v>
       </c>
@@ -15025,8 +14800,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K17" s="37"/>
-      <c r="L17" s="35"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="1"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5">
         <f t="shared" si="2"/>
@@ -15040,8 +14815,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="35"/>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="1"/>
       <c r="S17" s="5"/>
       <c r="T17" s="5">
         <f t="shared" si="4"/>
@@ -15055,8 +14830,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W17" s="37"/>
-      <c r="X17" s="35"/>
+      <c r="W17" s="5"/>
+      <c r="X17" s="1"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="5">
         <f t="shared" si="6"/>
@@ -15067,26 +14842,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A18" s="35">
+    <row r="18" spans="1:27" ht="20.25">
+      <c r="A18" s="1">
         <v>2</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="37">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="37"/>
-      <c r="F18" s="35"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="1"/>
       <c r="G18" s="5"/>
-      <c r="H18" s="37">
+      <c r="H18" s="5">
         <f>IF((D18-E18)&lt;0,0,(D18-E18))</f>
         <v>0</v>
       </c>
-      <c r="I18" s="37">
+      <c r="I18" s="5">
         <f>IF((E18-D18)&lt;0,0,(E18-D18))</f>
         <v>0</v>
       </c>
@@ -15094,8 +14869,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K18" s="37"/>
-      <c r="L18" s="35"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="1"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5">
         <f t="shared" si="2"/>
@@ -15109,8 +14884,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="35"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="1"/>
       <c r="S18" s="5"/>
       <c r="T18" s="5">
         <f t="shared" si="4"/>
@@ -15124,8 +14899,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W18" s="37"/>
-      <c r="X18" s="35"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="1"/>
       <c r="Y18" s="5"/>
       <c r="Z18" s="5">
         <f t="shared" si="6"/>
@@ -15136,26 +14911,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A19" s="35">
+    <row r="19" spans="1:27" ht="20.25">
+      <c r="A19" s="1">
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="37">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="37"/>
-      <c r="F19" s="35"/>
+        <v>70</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="1"/>
       <c r="G19" s="5"/>
-      <c r="H19" s="37">
+      <c r="H19" s="5">
         <f>IF((D19-E19)&lt;0,0,(D19-E19))</f>
         <v>0</v>
       </c>
-      <c r="I19" s="37">
+      <c r="I19" s="5">
         <f>IF((E19-D19)&lt;0,0,(E19-D19))</f>
         <v>0</v>
       </c>
@@ -15163,8 +14938,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K19" s="37"/>
-      <c r="L19" s="35"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="1"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5">
         <f t="shared" si="2"/>
@@ -15178,8 +14953,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="37"/>
-      <c r="R19" s="35"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="1"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
         <f t="shared" si="4"/>
@@ -15193,8 +14968,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W19" s="37"/>
-      <c r="X19" s="35"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="1"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="5">
         <f t="shared" si="6"/>
@@ -15205,10 +14980,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="44"/>
-    </row>
-    <row r="21" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" s="7" customFormat="1"/>
+    <row r="21" spans="1:27" ht="34.5">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -15277,7 +15050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="20.25">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -15346,7 +15119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="20.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15415,7 +15188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="20.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15484,7 +15257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="20.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15553,7 +15326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="20.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15622,26 +15395,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A27" s="35">
+    <row r="27" spans="1:27" ht="20.25">
+      <c r="A27" s="1">
         <v>3</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="35"/>
-      <c r="D27" s="37">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="37"/>
-      <c r="F27" s="35"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="5"/>
+      <c r="F27" s="1"/>
       <c r="G27" s="5"/>
-      <c r="H27" s="37">
+      <c r="H27" s="5">
         <f>IF((D27-E27)&lt;0,0,(D27-E27))</f>
         <v>0</v>
       </c>
-      <c r="I27" s="37">
+      <c r="I27" s="5">
         <f>IF((E27-D27)&lt;0,0,(E27-D27))</f>
         <v>0</v>
       </c>
@@ -15649,8 +15422,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K27" s="37"/>
-      <c r="L27" s="35"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="1"/>
       <c r="M27" s="5"/>
       <c r="N27" s="5">
         <f t="shared" si="2"/>
@@ -15664,8 +15437,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q27" s="37"/>
-      <c r="R27" s="35"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="1"/>
       <c r="S27" s="5"/>
       <c r="T27" s="5">
         <f t="shared" si="4"/>
@@ -15679,8 +15452,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W27" s="37"/>
-      <c r="X27" s="35"/>
+      <c r="W27" s="5"/>
+      <c r="X27" s="1"/>
       <c r="Y27" s="5"/>
       <c r="Z27" s="5">
         <f t="shared" si="6"/>
@@ -15691,26 +15464,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A28" s="35">
+    <row r="28" spans="1:27" ht="20.25">
+      <c r="A28" s="1">
         <v>3</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="35"/>
-      <c r="D28" s="37">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="37"/>
-      <c r="F28" s="35"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="5"/>
+      <c r="F28" s="1"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="37">
+      <c r="H28" s="5">
         <f>IF((D28-E28)&lt;0,0,(D28-E28))</f>
         <v>0</v>
       </c>
-      <c r="I28" s="37">
+      <c r="I28" s="5">
         <f>IF((E28-D28)&lt;0,0,(E28-D28))</f>
         <v>0</v>
       </c>
@@ -15718,8 +15491,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K28" s="37"/>
-      <c r="L28" s="35"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="1"/>
       <c r="M28" s="5"/>
       <c r="N28" s="5">
         <f t="shared" si="2"/>
@@ -15733,8 +15506,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q28" s="37"/>
-      <c r="R28" s="35"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="1"/>
       <c r="S28" s="5"/>
       <c r="T28" s="5">
         <f t="shared" si="4"/>
@@ -15748,8 +15521,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W28" s="37"/>
-      <c r="X28" s="35"/>
+      <c r="W28" s="5"/>
+      <c r="X28" s="1"/>
       <c r="Y28" s="5"/>
       <c r="Z28" s="5">
         <f t="shared" si="6"/>
@@ -15760,26 +15533,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A29" s="35">
+    <row r="29" spans="1:27" ht="20.25">
+      <c r="A29" s="1">
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" s="35"/>
-      <c r="D29" s="37">
-        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="37"/>
-      <c r="F29" s="35"/>
+        <v>70</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="5">
+        <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="5"/>
+      <c r="F29" s="1"/>
       <c r="G29" s="5"/>
-      <c r="H29" s="37">
+      <c r="H29" s="5">
         <f>IF((D29-E29)&lt;0,0,(D29-E29))</f>
         <v>0</v>
       </c>
-      <c r="I29" s="37">
+      <c r="I29" s="5">
         <f>IF((E29-D29)&lt;0,0,(E29-D29))</f>
         <v>0</v>
       </c>
@@ -15787,8 +15560,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K29" s="37"/>
-      <c r="L29" s="35"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="1"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5">
         <f t="shared" si="2"/>
@@ -15802,8 +15575,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q29" s="37"/>
-      <c r="R29" s="35"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="1"/>
       <c r="S29" s="5"/>
       <c r="T29" s="5">
         <f t="shared" si="4"/>
@@ -15817,8 +15590,8 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W29" s="37"/>
-      <c r="X29" s="35"/>
+      <c r="W29" s="5"/>
+      <c r="X29" s="1"/>
       <c r="Y29" s="5"/>
       <c r="Z29" s="5">
         <f t="shared" si="6"/>
@@ -15829,10 +15602,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="44"/>
-    </row>
-    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" s="7" customFormat="1"/>
+    <row r="31" spans="1:27" ht="20.25">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -15901,7 +15672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="20.25">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15970,7 +15741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="20.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -16039,7 +15810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="20.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -16108,7 +15879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="20.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -16177,7 +15948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="20.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -16246,12 +16017,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A37" s="46">
+    <row r="37" spans="1:27" ht="20.25">
+      <c r="A37" s="37">
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5">
@@ -16261,11 +16032,11 @@
       <c r="E37" s="5"/>
       <c r="F37" s="1"/>
       <c r="G37" s="5"/>
-      <c r="H37" s="47">
+      <c r="H37" s="5">
         <f>IF((D37-E37)&lt;0,0,(D37-E37))</f>
         <v>0</v>
       </c>
-      <c r="I37" s="47">
+      <c r="I37" s="5">
         <f>IF((E37-D37)&lt;0,0,(E37-D37))</f>
         <v>0</v>
       </c>
@@ -16315,12 +16086,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="20.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -16384,7 +16155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="20.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16453,12 +16224,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A40" s="46">
+    <row r="40" spans="1:27" ht="20.25">
+      <c r="A40" s="37">
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5">
@@ -16468,11 +16239,11 @@
       <c r="E40" s="5"/>
       <c r="F40" s="1"/>
       <c r="G40" s="5"/>
-      <c r="H40" s="47">
+      <c r="H40" s="5">
         <f>IF((D40-E40)&lt;0,0,(D40-E40))</f>
         <v>0</v>
       </c>
-      <c r="I40" s="47">
+      <c r="I40" s="5">
         <f>IF((E40-D40)&lt;0,0,(E40-D40))</f>
         <v>0</v>
       </c>
@@ -16522,12 +16293,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="20.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="5">
@@ -16591,10 +16362,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="44"/>
-    </row>
-    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" s="7" customFormat="1"/>
+    <row r="43" spans="1:27" ht="20.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -16663,7 +16432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="20.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16732,7 +16501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" ht="20.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16801,7 +16570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" ht="20.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16870,7 +16639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" ht="20.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16939,7 +16708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" ht="20.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -17008,12 +16777,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A49" s="46">
+    <row r="49" spans="1:27" ht="20.25">
+      <c r="A49" s="37">
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5">
@@ -17023,11 +16792,11 @@
       <c r="E49" s="5"/>
       <c r="F49" s="1"/>
       <c r="G49" s="5"/>
-      <c r="H49" s="47">
+      <c r="H49" s="5">
         <f>IF((D49-E49)&lt;0,0,(D49-E49))</f>
         <v>0</v>
       </c>
-      <c r="I49" s="47">
+      <c r="I49" s="5">
         <f>IF((E49-D49)&lt;0,0,(E49-D49))</f>
         <v>0</v>
       </c>
@@ -17077,12 +16846,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" ht="20.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="5">
@@ -17146,7 +16915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" ht="20.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -17215,12 +16984,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A52" s="46">
+    <row r="52" spans="1:27" ht="20.25">
+      <c r="A52" s="37">
         <v>5</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5">
@@ -17230,11 +16999,11 @@
       <c r="E52" s="5"/>
       <c r="F52" s="1"/>
       <c r="G52" s="5"/>
-      <c r="H52" s="47">
+      <c r="H52" s="5">
         <f>IF((D52-E52)&lt;0,0,(D52-E52))</f>
         <v>0</v>
       </c>
-      <c r="I52" s="47">
+      <c r="I52" s="5">
         <f>IF((E52-D52)&lt;0,0,(E52-D52))</f>
         <v>0</v>
       </c>
@@ -17284,12 +17053,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" ht="20.25">
       <c r="A53" s="1">
         <v>5</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -17353,10 +17122,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="44"/>
-    </row>
-    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" s="7" customFormat="1"/>
+    <row r="55" spans="1:27" ht="20.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17425,7 +17192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" ht="20.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17494,7 +17261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" ht="20.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17563,7 +17330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" ht="20.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17632,7 +17399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" ht="20.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17701,7 +17468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" ht="20.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17770,12 +17537,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A61" s="46">
+    <row r="61" spans="1:27" ht="20.25">
+      <c r="A61" s="37">
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5">
@@ -17785,11 +17552,11 @@
       <c r="E61" s="5"/>
       <c r="F61" s="1"/>
       <c r="G61" s="5"/>
-      <c r="H61" s="47">
+      <c r="H61" s="5">
         <f>IF((D61-E61)&lt;0,0,(D61-E61))</f>
         <v>0</v>
       </c>
-      <c r="I61" s="47">
+      <c r="I61" s="5">
         <f>IF((E61-D61)&lt;0,0,(E61-D61))</f>
         <v>0</v>
       </c>
@@ -17839,12 +17606,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" ht="20.25">
       <c r="A62" s="1">
         <v>6</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="5">
@@ -17908,7 +17675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" ht="20.25">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -17977,12 +17744,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A64" s="46">
+    <row r="64" spans="1:27" ht="20.25">
+      <c r="A64" s="37">
         <v>6</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5">
@@ -17992,11 +17759,11 @@
       <c r="E64" s="5"/>
       <c r="F64" s="1"/>
       <c r="G64" s="5"/>
-      <c r="H64" s="47">
+      <c r="H64" s="5">
         <f>IF((D64-E64)&lt;0,0,(D64-E64))</f>
         <v>0</v>
       </c>
-      <c r="I64" s="47">
+      <c r="I64" s="5">
         <f>IF((E64-D64)&lt;0,0,(E64-D64))</f>
         <v>0</v>
       </c>
@@ -18046,12 +17813,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" ht="20.25">
       <c r="A65" s="1">
         <v>6</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="5">
@@ -18115,10 +17882,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="44"/>
-    </row>
-    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" s="7" customFormat="1"/>
+    <row r="67" spans="1:27" ht="20.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -18187,7 +17952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" ht="20.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -18256,7 +18021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" ht="20.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -18325,12 +18090,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" ht="20.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C70" s="10"/>
       <c r="D70" s="12">
@@ -18394,7 +18159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" ht="20.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18463,7 +18228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" ht="20.25">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18532,12 +18297,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A73" s="48">
+    <row r="73" spans="1:27" ht="20.25">
+      <c r="A73" s="38">
         <v>7</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C73" s="12"/>
       <c r="D73" s="12">
@@ -18547,11 +18312,11 @@
       <c r="E73" s="12"/>
       <c r="F73" s="10"/>
       <c r="G73" s="12"/>
-      <c r="H73" s="50">
+      <c r="H73" s="12">
         <f>IF((D73-E73)&lt;0,0,(D73-E73))</f>
         <v>0</v>
       </c>
-      <c r="I73" s="50">
+      <c r="I73" s="12">
         <f>IF((E73-D73)&lt;0,0,(E73-D73))</f>
         <v>0</v>
       </c>
@@ -18601,12 +18366,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" ht="20.25">
       <c r="A74" s="10">
         <v>7</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -18670,12 +18435,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" ht="20.25">
       <c r="A75" s="10">
         <v>7</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="12">
@@ -18739,12 +18504,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A76" s="48">
+    <row r="76" spans="1:27" ht="20.25">
+      <c r="A76" s="38">
         <v>7</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C76" s="12"/>
       <c r="D76" s="12">
@@ -18754,11 +18519,11 @@
       <c r="E76" s="12"/>
       <c r="F76" s="10"/>
       <c r="G76" s="12"/>
-      <c r="H76" s="50">
+      <c r="H76" s="12">
         <f>IF((D76-E76)&lt;0,0,(D76-E76))</f>
         <v>0</v>
       </c>
-      <c r="I76" s="50">
+      <c r="I76" s="12">
         <f>IF((E76-D76)&lt;0,0,(E76-D76))</f>
         <v>0</v>
       </c>
@@ -18808,12 +18573,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" ht="20.25">
       <c r="A77" s="10">
         <v>7</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="12">
@@ -18877,10 +18642,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="44"/>
-    </row>
-    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" s="7" customFormat="1"/>
+    <row r="79" spans="1:27" ht="20.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -18949,7 +18712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" ht="20.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -19018,7 +18781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" ht="20.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -19087,12 +18850,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" ht="20.25">
       <c r="A82" s="10">
         <v>8</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="12">
@@ -19156,12 +18919,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" ht="20.25">
       <c r="A83" s="10">
         <v>8</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="12">
@@ -19225,7 +18988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" ht="20.25">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -19294,12 +19057,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A85" s="48">
+    <row r="85" spans="1:27" ht="20.25">
+      <c r="A85" s="38">
         <v>8</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C85" s="12"/>
       <c r="D85" s="12">
@@ -19309,11 +19072,11 @@
       <c r="E85" s="12"/>
       <c r="F85" s="10"/>
       <c r="G85" s="12"/>
-      <c r="H85" s="50">
+      <c r="H85" s="12">
         <f>IF((D85-E85)&lt;0,0,(D85-E85))</f>
         <v>0</v>
       </c>
-      <c r="I85" s="50">
+      <c r="I85" s="12">
         <f>IF((E85-D85)&lt;0,0,(E85-D85))</f>
         <v>0</v>
       </c>
@@ -19363,12 +19126,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" ht="20.25">
       <c r="A86" s="10">
         <v>8</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="12">
@@ -19432,12 +19195,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" ht="20.25">
       <c r="A87" s="10">
         <v>8</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="12">
@@ -19501,12 +19264,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A88" s="48">
+    <row r="88" spans="1:27" ht="20.25">
+      <c r="A88" s="38">
         <v>8</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C88" s="12"/>
       <c r="D88" s="12">
@@ -19516,11 +19279,11 @@
       <c r="E88" s="12"/>
       <c r="F88" s="10"/>
       <c r="G88" s="12"/>
-      <c r="H88" s="50">
+      <c r="H88" s="12">
         <f>IF((D88-E88)&lt;0,0,(D88-E88))</f>
         <v>0</v>
       </c>
-      <c r="I88" s="50">
+      <c r="I88" s="12">
         <f>IF((E88-D88)&lt;0,0,(E88-D88))</f>
         <v>0</v>
       </c>
@@ -19570,12 +19333,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" ht="20.25">
       <c r="A89" s="10">
         <v>8</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="12">
@@ -19639,10 +19402,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B90" s="44"/>
-    </row>
-    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" s="7" customFormat="1"/>
+    <row r="91" spans="1:27" ht="20.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -19711,7 +19472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" ht="20.25">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19780,7 +19541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" ht="20.25">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19849,12 +19610,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" ht="20.25">
       <c r="A94" s="10">
         <v>9</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -19918,12 +19679,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" ht="20.25">
       <c r="A95" s="10">
         <v>9</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="12">
@@ -19987,7 +19748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" ht="20.25">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -20056,12 +19817,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A97" s="48">
+    <row r="97" spans="1:27" ht="20.25">
+      <c r="A97" s="38">
         <v>9</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="12">
@@ -20071,11 +19832,11 @@
       <c r="E97" s="12"/>
       <c r="F97" s="10"/>
       <c r="G97" s="12"/>
-      <c r="H97" s="50">
+      <c r="H97" s="12">
         <f>IF((D97-E97)&lt;0,0,(D97-E97))</f>
         <v>0</v>
       </c>
-      <c r="I97" s="50">
+      <c r="I97" s="12">
         <f>IF((E97-D97)&lt;0,0,(E97-D97))</f>
         <v>0</v>
       </c>
@@ -20125,12 +19886,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" ht="20.25">
       <c r="A98" s="10">
         <v>9</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -20194,12 +19955,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" ht="20.25">
       <c r="A99" s="10">
         <v>9</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="12">
@@ -20263,12 +20024,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A100" s="48">
+    <row r="100" spans="1:27" ht="20.25">
+      <c r="A100" s="38">
         <v>9</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -20278,11 +20039,11 @@
       <c r="E100" s="12"/>
       <c r="F100" s="10"/>
       <c r="G100" s="12"/>
-      <c r="H100" s="50">
+      <c r="H100" s="12">
         <f>IF((D100-E100)&lt;0,0,(D100-E100))</f>
         <v>0</v>
       </c>
-      <c r="I100" s="50">
+      <c r="I100" s="12">
         <f>IF((E100-D100)&lt;0,0,(E100-D100))</f>
         <v>0</v>
       </c>
@@ -20332,12 +20093,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" ht="20.25">
       <c r="A101" s="10">
         <v>9</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="12">
@@ -20401,10 +20162,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B102" s="44"/>
-    </row>
-    <row r="103" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:27" s="7" customFormat="1"/>
+    <row r="103" spans="1:27" ht="20.25">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20473,7 +20232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" ht="20.25">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20542,7 +20301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" ht="20.25">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20611,12 +20370,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" ht="20.25">
       <c r="A106" s="10">
         <v>10</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C106" s="10"/>
       <c r="D106" s="12">
@@ -20680,12 +20439,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" ht="20.25">
       <c r="A107" s="10">
         <v>10</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="12">
@@ -20749,7 +20508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" ht="20.25">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20818,12 +20577,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A109" s="48">
+    <row r="109" spans="1:27" ht="20.25">
+      <c r="A109" s="38">
         <v>10</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="12">
@@ -20833,11 +20592,11 @@
       <c r="E109" s="12"/>
       <c r="F109" s="10"/>
       <c r="G109" s="12"/>
-      <c r="H109" s="50">
+      <c r="H109" s="12">
         <f>IF((D109-E109)&lt;0,0,(D109-E109))</f>
         <v>0</v>
       </c>
-      <c r="I109" s="50">
+      <c r="I109" s="12">
         <f>IF((E109-D109)&lt;0,0,(E109-D109))</f>
         <v>0</v>
       </c>
@@ -20887,12 +20646,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" ht="20.25">
       <c r="A110" s="10">
         <v>10</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C110" s="10"/>
       <c r="D110" s="12">
@@ -20956,12 +20715,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" ht="20.25">
       <c r="A111" s="10">
         <v>10</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="12">
@@ -21025,12 +20784,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A112" s="48">
+    <row r="112" spans="1:27" ht="20.25">
+      <c r="A112" s="38">
         <v>10</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C112" s="10"/>
       <c r="D112" s="12">
@@ -21040,11 +20799,11 @@
       <c r="E112" s="12"/>
       <c r="F112" s="10"/>
       <c r="G112" s="12"/>
-      <c r="H112" s="50">
+      <c r="H112" s="12">
         <f>IF((D112-E112)&lt;0,0,(D112-E112))</f>
         <v>0</v>
       </c>
-      <c r="I112" s="50">
+      <c r="I112" s="12">
         <f>IF((E112-D112)&lt;0,0,(E112-D112))</f>
         <v>0</v>
       </c>
@@ -21094,12 +20853,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:28" ht="20.25">
       <c r="A113" s="10">
         <v>10</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="12">
@@ -21163,15 +20922,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B114" s="44"/>
-    </row>
-    <row r="115" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:28" s="7" customFormat="1"/>
+    <row r="115" spans="1:28" ht="34.5">
       <c r="A115" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="5">
@@ -21235,12 +20992,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:28" ht="20.25">
       <c r="A116" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="5">
@@ -21304,12 +21061,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:28" ht="20.25">
       <c r="A117" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="5">
@@ -21373,12 +21130,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:28" ht="20.25">
       <c r="A118" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="5">
@@ -21442,12 +21199,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:28" ht="34.5">
       <c r="A119" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="5">
@@ -21511,12 +21268,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:28" ht="34.5">
       <c r="A120" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="5">
@@ -21580,12 +21337,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:28" ht="34.5">
       <c r="A121" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="5">
@@ -21649,12 +21406,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:28" ht="38.25">
       <c r="A122" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="5">
@@ -21718,12 +21475,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B123" s="44"/>
-    </row>
-    <row r="124" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:28" s="7" customFormat="1"/>
+    <row r="124" spans="1:28">
       <c r="A124" s="7"/>
-      <c r="B124" s="44"/>
+      <c r="B124" s="7"/>
       <c r="C124" s="7"/>
       <c r="D124" s="7"/>
       <c r="E124" s="7"/>
@@ -21751,9 +21506,9 @@
       <c r="AA124" s="7"/>
       <c r="AB124" s="7"/>
     </row>
-    <row r="125" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:28">
       <c r="A125" s="7"/>
-      <c r="B125" s="44"/>
+      <c r="B125" s="7"/>
       <c r="C125" s="7"/>
       <c r="D125" s="7"/>
       <c r="E125" s="7"/>
@@ -21781,9 +21536,9 @@
       <c r="AA125" s="7"/>
       <c r="AB125" s="7"/>
     </row>
-    <row r="126" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:28">
       <c r="A126" s="7"/>
-      <c r="B126" s="44"/>
+      <c r="B126" s="7"/>
       <c r="C126" s="7"/>
       <c r="D126" s="7"/>
       <c r="E126" s="7"/>
@@ -21811,9 +21566,9 @@
       <c r="AA126" s="7"/>
       <c r="AB126" s="7"/>
     </row>
-    <row r="127" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:28">
       <c r="A127" s="7"/>
-      <c r="B127" s="44"/>
+      <c r="B127" s="7"/>
       <c r="C127" s="7"/>
       <c r="D127" s="7"/>
       <c r="E127" s="7"/>
@@ -21841,9 +21596,9 @@
       <c r="AA127" s="7"/>
       <c r="AB127" s="7"/>
     </row>
-    <row r="128" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:28">
       <c r="A128" s="7"/>
-      <c r="B128" s="44"/>
+      <c r="B128" s="7"/>
       <c r="C128" s="7"/>
       <c r="D128" s="7"/>
       <c r="E128" s="7"/>
@@ -21871,9 +21626,9 @@
       <c r="AA128" s="7"/>
       <c r="AB128" s="7"/>
     </row>
-    <row r="129" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:28">
       <c r="A129" s="7"/>
-      <c r="B129" s="44"/>
+      <c r="B129" s="7"/>
       <c r="C129" s="7"/>
       <c r="D129" s="7"/>
       <c r="E129" s="7"/>
@@ -21901,9 +21656,9 @@
       <c r="AA129" s="7"/>
       <c r="AB129" s="7"/>
     </row>
-    <row r="130" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:28">
       <c r="A130" s="7"/>
-      <c r="B130" s="44"/>
+      <c r="B130" s="7"/>
       <c r="C130" s="7"/>
       <c r="D130" s="7"/>
       <c r="E130" s="7"/>
@@ -21931,9 +21686,9 @@
       <c r="AA130" s="7"/>
       <c r="AB130" s="7"/>
     </row>
-    <row r="131" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:28">
       <c r="A131" s="7"/>
-      <c r="B131" s="44"/>
+      <c r="B131" s="7"/>
       <c r="C131" s="7"/>
       <c r="D131" s="7"/>
       <c r="E131" s="7"/>
@@ -21961,9 +21716,9 @@
       <c r="AA131" s="7"/>
       <c r="AB131" s="7"/>
     </row>
-    <row r="132" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:28">
       <c r="A132" s="7"/>
-      <c r="B132" s="44"/>
+      <c r="B132" s="7"/>
       <c r="C132" s="7"/>
       <c r="D132" s="7"/>
       <c r="E132" s="7"/>
@@ -21991,9 +21746,9 @@
       <c r="AA132" s="7"/>
       <c r="AB132" s="7"/>
     </row>
-    <row r="133" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:28">
       <c r="A133" s="7"/>
-      <c r="B133" s="44"/>
+      <c r="B133" s="7"/>
       <c r="C133" s="7"/>
       <c r="D133" s="7"/>
       <c r="E133" s="7"/>
@@ -22021,9 +21776,9 @@
       <c r="AA133" s="7"/>
       <c r="AB133" s="7"/>
     </row>
-    <row r="134" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:28">
       <c r="A134" s="7"/>
-      <c r="B134" s="44"/>
+      <c r="B134" s="7"/>
       <c r="C134" s="7"/>
       <c r="D134" s="7"/>
       <c r="E134" s="7"/>
@@ -22051,9 +21806,9 @@
       <c r="AA134" s="7"/>
       <c r="AB134" s="7"/>
     </row>
-    <row r="135" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:28">
       <c r="A135" s="7"/>
-      <c r="B135" s="44"/>
+      <c r="B135" s="7"/>
       <c r="C135" s="7"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7"/>
@@ -22081,9 +21836,9 @@
       <c r="AA135" s="7"/>
       <c r="AB135" s="7"/>
     </row>
-    <row r="136" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:28">
       <c r="A136" s="7"/>
-      <c r="B136" s="44"/>
+      <c r="B136" s="7"/>
       <c r="C136" s="7"/>
       <c r="D136" s="7"/>
       <c r="E136" s="7"/>
@@ -22111,9 +21866,9 @@
       <c r="AA136" s="7"/>
       <c r="AB136" s="7"/>
     </row>
-    <row r="137" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:28">
       <c r="A137" s="7"/>
-      <c r="B137" s="44"/>
+      <c r="B137" s="7"/>
       <c r="C137" s="7"/>
       <c r="D137" s="7"/>
       <c r="E137" s="7"/>
@@ -22141,9 +21896,9 @@
       <c r="AA137" s="7"/>
       <c r="AB137" s="7"/>
     </row>
-    <row r="138" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:28">
       <c r="A138" s="7"/>
-      <c r="B138" s="44"/>
+      <c r="B138" s="7"/>
       <c r="C138" s="7"/>
       <c r="D138" s="7"/>
       <c r="E138" s="7"/>
@@ -22171,9 +21926,9 @@
       <c r="AA138" s="7"/>
       <c r="AB138" s="7"/>
     </row>
-    <row r="139" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:28">
       <c r="A139" s="7"/>
-      <c r="B139" s="44"/>
+      <c r="B139" s="7"/>
       <c r="C139" s="7"/>
       <c r="D139" s="7"/>
       <c r="E139" s="7"/>
@@ -22201,9 +21956,9 @@
       <c r="AA139" s="7"/>
       <c r="AB139" s="7"/>
     </row>
-    <row r="140" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:28">
       <c r="A140" s="7"/>
-      <c r="B140" s="44"/>
+      <c r="B140" s="7"/>
       <c r="C140" s="7"/>
       <c r="D140" s="7"/>
       <c r="E140" s="7"/>
@@ -22231,186 +21986,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10" x14ac:dyDescent="0.2">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22428,8 +22003,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
